--- a/assignment01/Excel GRAPH/Task04Recurrence_T1_T2_Analysis.xlsx
+++ b/assignment01/Excel GRAPH/Task04Recurrence_T1_T2_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CollageSem4\ADA\assignment01\Excel GRAPH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C3DAFE0-383E-458A-A803-CEBF9A2F3BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC77391-7F93-47E4-A7A4-F32856B152A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1280,15 +1280,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>121920</xdr:colOff>
+      <xdr:colOff>137160</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>426720</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
